--- a/tests/sample_artifacts/invalid/excel/invalid_missing_tabs.xlsx
+++ b/tests/sample_artifacts/invalid/excel/invalid_missing_tabs.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,25 +441,218 @@
           <t>CreditLimit</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IsActive</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RegionCode</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SourceSystem</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CUST81001</t>
+          <t>CUST01100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Only One Tab</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
+          <t>Customer 1100</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>45299</v>
       </c>
       <c r="D2" t="n">
-        <v>1000</v>
+        <v>1550</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CUST01101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer 1101</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>45300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1585.75</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CUST01102</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer 1102</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1621.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CUST01103</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer 1103</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>45302</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1657.25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CUST01104</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer 1104</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>45303</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1693</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CUST01105</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer 1105</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>45304</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1728.75</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
       </c>
     </row>
   </sheetData>
